--- a/knowledge-base/02-财务处/常见问题/财务报销常见问题.xlsx
+++ b/knowledge-base/02-财务处/常见问题/财务报销常见问题.xlsx
@@ -1,52 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="财务报销FAQ" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="财务报销FAQ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -65,13 +42,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -396,67 +440,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>问题</v>
-      </c>
-      <c r="B1" t="str">
-        <v>答案</v>
-      </c>
-      <c r="C1" t="str">
-        <v>同义问法</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>答案</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>同义问法</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>发票丢失了还能报销吗？</v>
-      </c>
-      <c r="B2" t="str">
-        <v>可以。票据遗失的，需提供票据复印件或电子发票打印件，并填写《票据遗失情况说明》，经单位负责人签字后按流程报销；无法提供任何凭证的部分不予报销。</v>
-      </c>
-      <c r="C2" t="str">
-        <v>发票丢了怎么办;没有发票能报吗;票据遗失如何处理</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>发票丢失了还能报销吗？</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>可以。票据遗失的，需提供票据复印件或电子发票打印件，并填写《票据遗失情况说明》，经单位负责人签字后按流程报销；无法提供任何凭证的部分不予报销。</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>发票丢了怎么办;没有发票能报吗;票据遗失如何处理</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>网上报销系统忘记密码怎么办？</v>
-      </c>
-      <c r="B3" t="str">
-        <v>持本人身份证到财务处报销科重置，或通过网上办事大厅"密码找回"功能自助重置。</v>
-      </c>
-      <c r="C3" t="str">
-        <v>报销系统密码忘了;报销平台登录不了</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>网上报销系统忘记密码怎么办？</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>持本人身份证到财务处报销科重置，或通过网上办事大厅"密码找回"功能自助重置。</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>报销系统密码忘了;报销平台登录不了</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>报销款多久到账？</v>
-      </c>
-      <c r="B4" t="str">
-        <v>财务审核通过后一般 5-10 个工作日到账；年底集中报销期间可能延长至 15 个工作日。</v>
-      </c>
-      <c r="C4" t="str">
-        <v>钱什么时候到账;报销进度怎么查;报销款为什么还没到</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>报销款多久到账？</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>财务审核通过后一般 5-10 个工作日到账；年底集中报销期间可能延长至 15 个工作日。</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>钱什么时候到账;报销进度怎么查;报销款为什么还没到</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>学生可以报销科研经费吗？</v>
-      </c>
-      <c r="B5" t="str">
-        <v>可以。学生参与导师课题出差，费用可在导师科研经费中报销，出差审批单须由导师签字确认。</v>
-      </c>
-      <c r="C5" t="str">
-        <v>学生出差怎么报销;研究生能报科研经费吗</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>学生可以报销科研经费吗？</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>可以。学生参与导师课题出差，费用可在导师科研经费中报销，出差审批单须由导师签字确认。</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>学生出差怎么报销;研究生能报科研经费吗</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>